--- a/cet4/result/78_医道女神_白衣天使的仁心/78_医道女神_白衣天使的仁心_学习版.xlsx
+++ b/cet4/result/78_医道女神_白衣天使的仁心/78_医道女神_白衣天使的仁心_学习版.xlsx
@@ -397,843 +397,703 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D49"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>morning</v>
       </c>
       <c r="B2" t="str">
-        <v>morning</v>
+        <v>/ˈmɔːrnɪŋ/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>早晨</v>
       </c>
-      <c r="D2" t="str">
-        <v>morning(早晨)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>physician</v>
       </c>
       <c r="B3" t="str">
-        <v>physician</v>
+        <v>/fɪˈzɪʃn/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>内科医师</v>
       </c>
-      <c r="D3" t="str">
-        <v>physician(内科医师)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>leading</v>
       </c>
       <c r="B4" t="str">
-        <v>leading</v>
+        <v>/ˈliːdɪŋ; ˈledɪŋ/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./v./adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>主要的</v>
       </c>
-      <c r="D4" t="str">
-        <v>leading(主要的)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>complaint</v>
       </c>
       <c r="B5" t="str">
-        <v>complaint</v>
+        <v>/kəmˈpleɪnt/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>疾病</v>
       </c>
-      <c r="D5" t="str">
-        <v>complaint(疾病)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>poverty</v>
       </c>
       <c r="B6" t="str">
-        <v>poverty</v>
+        <v>/ˈpɑːvərti/</v>
       </c>
       <c r="C6" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>贫困</v>
       </c>
-      <c r="D6" t="str">
-        <v>poverty(贫困)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>comfort</v>
       </c>
       <c r="B7" t="str">
-        <v>comfort</v>
+        <v>/ˈkʌmfərt/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D7" t="str">
         <v>安慰</v>
       </c>
-      <c r="D7" t="str">
-        <v>comfort(安慰)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>certificate</v>
       </c>
       <c r="B8" t="str">
-        <v>certificate</v>
+        <v>/sərˈtɪfɪkət/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D8" t="str">
         <v>证书</v>
       </c>
-      <c r="D8" t="str">
-        <v>certificate(证书)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>comprehensive</v>
       </c>
       <c r="B9" t="str">
-        <v>comprehensive</v>
+        <v>/ˌkɑːmprɪˈhensɪv/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>综合的</v>
       </c>
-      <c r="D9" t="str">
-        <v>comprehensive(综合的)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>conjunction</v>
       </c>
       <c r="B10" t="str">
-        <v>conjunction</v>
+        <v>/kənˈdʒʌŋkʃn/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>结合</v>
       </c>
-      <c r="D10" t="str">
-        <v>conjunction(结合)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>destruction</v>
       </c>
       <c r="B11" t="str">
-        <v>destruction</v>
+        <v>/dɪˈstrʌkʃn/</v>
       </c>
       <c r="C11" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>破坏</v>
       </c>
-      <c r="D11" t="str">
-        <v>destruction(破坏)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>straight</v>
       </c>
       <c r="B12" t="str">
-        <v>straight</v>
+        <v>/streɪt/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./adj./adv.</v>
+      </c>
+      <c r="D12" t="str">
         <v>直的</v>
       </c>
-      <c r="D12" t="str">
-        <v>straight(直的)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>procedure</v>
       </c>
       <c r="B13" t="str">
-        <v>procedure</v>
+        <v>/prəˈsiːdʒər/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>步骤</v>
       </c>
-      <c r="D13" t="str">
-        <v>procedure(步骤)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>twice</v>
       </c>
       <c r="B14" t="str">
-        <v>twice</v>
+        <v>/twaɪs/</v>
       </c>
       <c r="C14" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D14" t="str">
         <v>两次</v>
       </c>
-      <c r="D14" t="str">
-        <v>twice(两次)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>prevail</v>
       </c>
       <c r="B15" t="str">
-        <v>prevail</v>
+        <v>/prɪˈveɪl/</v>
       </c>
       <c r="C15" t="str">
+        <v>vi.</v>
+      </c>
+      <c r="D15" t="str">
         <v>获胜</v>
       </c>
-      <c r="D15" t="str">
-        <v>prevail(获胜)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>hero</v>
       </c>
       <c r="B16" t="str">
-        <v>hero</v>
+        <v>/ˈhɪroʊ,ˈhiːroʊ/</v>
       </c>
       <c r="C16" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>英雄</v>
       </c>
-      <c r="D16" t="str">
-        <v>hero(英雄)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>method</v>
       </c>
       <c r="B17" t="str">
-        <v>procedure</v>
+        <v>/ˈmeθəd/</v>
       </c>
       <c r="C17" t="str">
-        <v>手续</v>
+        <v>n.</v>
       </c>
       <c r="D17" t="str">
-        <v>procedure(手续)📢</v>
+        <v>方法</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>congress</v>
       </c>
       <c r="B18" t="str">
-        <v>method</v>
+        <v>/ˈkɑːŋɡrəs/</v>
       </c>
       <c r="C18" t="str">
-        <v>方法</v>
+        <v>n.</v>
       </c>
       <c r="D18" t="str">
-        <v>method(方法)📢</v>
+        <v>代表大会</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>readily</v>
       </c>
       <c r="B19" t="str">
-        <v>congress</v>
+        <v>/ˈredɪli/</v>
       </c>
       <c r="C19" t="str">
-        <v>代表大会</v>
+        <v>v./adv.</v>
       </c>
       <c r="D19" t="str">
-        <v>congress(代表大会)📢</v>
+        <v>乐意地</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>curious</v>
       </c>
       <c r="B20" t="str">
-        <v>readily</v>
+        <v>/ˈkjʊriəs/</v>
       </c>
       <c r="C20" t="str">
-        <v>乐意地</v>
+        <v>adj.</v>
       </c>
       <c r="D20" t="str">
-        <v>readily(乐意地)📢</v>
+        <v>好奇的</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>brain</v>
       </c>
       <c r="B21" t="str">
-        <v>curious</v>
+        <v>/breɪn/</v>
       </c>
       <c r="C21" t="str">
-        <v>好奇的</v>
+        <v>n./vt.</v>
       </c>
       <c r="D21" t="str">
-        <v>curious(好奇的)📢</v>
+        <v>头脑</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>arithmetic</v>
       </c>
       <c r="B22" t="str">
-        <v>brain</v>
+        <v>/əˈrɪθmətɪk/</v>
       </c>
       <c r="C22" t="str">
-        <v>头脑</v>
+        <v>n.</v>
       </c>
       <c r="D22" t="str">
-        <v>brain(头脑)📢</v>
+        <v>算术</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>forecast</v>
       </c>
       <c r="B23" t="str">
-        <v>arithmetic</v>
+        <v>/ˈfɔːrkæst/</v>
       </c>
       <c r="C23" t="str">
-        <v>算术</v>
+        <v>n./v.</v>
       </c>
       <c r="D23" t="str">
-        <v>arithmetic(算术)📢</v>
+        <v>预测</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>unlucky</v>
       </c>
       <c r="B24" t="str">
-        <v>forecast</v>
+        <v>/ʌnˈlʌki/</v>
       </c>
       <c r="C24" t="str">
-        <v>预测</v>
+        <v>adj.</v>
       </c>
       <c r="D24" t="str">
-        <v>forecast(预测)📢</v>
+        <v>不幸的</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>indifferent</v>
       </c>
       <c r="B25" t="str">
-        <v>unlucky</v>
+        <v>/ɪnˈdɪfrənt/</v>
       </c>
       <c r="C25" t="str">
-        <v>不幸的</v>
+        <v>n./adj.</v>
       </c>
       <c r="D25" t="str">
-        <v>unlucky(不幸的)📢</v>
+        <v>冷漠的</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>product</v>
       </c>
       <c r="B26" t="str">
-        <v>complaint</v>
+        <v>/ˈprɑːdʌkt/</v>
       </c>
       <c r="C26" t="str">
-        <v>抱怨</v>
+        <v>n.</v>
       </c>
       <c r="D26" t="str">
-        <v>complaint(抱怨)📢</v>
+        <v>结果</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>steadily</v>
       </c>
       <c r="B27" t="str">
-        <v>indifferent</v>
+        <v>/ˈstedəli/</v>
       </c>
       <c r="C27" t="str">
-        <v>冷漠的</v>
+        <v>v./adv.</v>
       </c>
       <c r="D27" t="str">
-        <v>indifferent(冷漠的)📢</v>
+        <v>稳定地</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>encounter</v>
       </c>
       <c r="B28" t="str">
-        <v>product</v>
+        <v>/ɪnˈkaʊntər/</v>
       </c>
       <c r="C28" t="str">
-        <v>结果</v>
+        <v>n./v.</v>
       </c>
       <c r="D28" t="str">
-        <v>product(结果)📢</v>
+        <v>遭遇</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>restaurant</v>
       </c>
       <c r="B29" t="str">
-        <v>steadily</v>
+        <v>/ˈrestrɑːnt,ˈrestərɑːnt/</v>
       </c>
       <c r="C29" t="str">
-        <v>稳定地</v>
+        <v>n.</v>
       </c>
       <c r="D29" t="str">
-        <v>steadily(稳定地)📢</v>
+        <v>餐馆</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>reflexion</v>
       </c>
       <c r="B30" t="str">
-        <v>comfort</v>
+        <v>/rɪˈflekʃn/</v>
       </c>
       <c r="C30" t="str">
-        <v>安慰</v>
+        <v>n.</v>
       </c>
       <c r="D30" t="str">
-        <v>comfort(安慰)📢</v>
+        <v>沉思</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>really</v>
       </c>
       <c r="B31" t="str">
-        <v>encounter</v>
+        <v>/ˈriːəli/</v>
       </c>
       <c r="C31" t="str">
-        <v>遭遇</v>
+        <v>v./adv.</v>
       </c>
       <c r="D31" t="str">
-        <v>encounter(遭遇)📢</v>
+        <v>真正</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>industrial</v>
       </c>
       <c r="B32" t="str">
-        <v>restaurant</v>
+        <v>/ɪnˈdʌstriəl/</v>
       </c>
       <c r="C32" t="str">
-        <v>餐馆</v>
+        <v>n./adj.</v>
       </c>
       <c r="D32" t="str">
-        <v>restaurant(餐馆)📢</v>
+        <v>工业的</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>bath</v>
       </c>
       <c r="B33" t="str">
-        <v>reflexion</v>
+        <v>/bæθ/</v>
       </c>
       <c r="C33" t="str">
-        <v>沉思</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D33" t="str">
-        <v>reflexion(沉思)📢</v>
+        <v>澡</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>carrier</v>
       </c>
       <c r="B34" t="str">
-        <v>really</v>
+        <v>/ˈkæriər/</v>
       </c>
       <c r="C34" t="str">
-        <v>真正</v>
+        <v>n.</v>
       </c>
       <c r="D34" t="str">
-        <v>really(真正)📢</v>
+        <v>运送者</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>airplane</v>
       </c>
       <c r="B35" t="str">
-        <v>industrial</v>
+        <v>/ˈerpleɪn/</v>
       </c>
       <c r="C35" t="str">
-        <v>工业的</v>
+        <v>n.</v>
       </c>
       <c r="D35" t="str">
-        <v>industrial(工业的)📢</v>
+        <v>飞机</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>gum</v>
       </c>
       <c r="B36" t="str">
-        <v>really</v>
+        <v>/ɡʌm/</v>
       </c>
       <c r="C36" t="str">
-        <v>真正</v>
+        <v>n./vt.</v>
       </c>
       <c r="D36" t="str">
-        <v>really(真正)📢</v>
+        <v>牙龈</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>grain</v>
       </c>
       <c r="B37" t="str">
-        <v>bath</v>
+        <v>/ɡreɪn/</v>
       </c>
       <c r="C37" t="str">
-        <v>澡</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D37" t="str">
-        <v>bath(澡)📢</v>
+        <v>谷物</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>needle</v>
       </c>
       <c r="B38" t="str">
-        <v>carrier</v>
+        <v>/ˈniːdl/</v>
       </c>
       <c r="C38" t="str">
-        <v>运送者</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D38" t="str">
-        <v>carrier(运送者)📢</v>
+        <v>针</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>tractor</v>
       </c>
       <c r="B39" t="str">
-        <v>airplane</v>
+        <v>/ˈtræktər/</v>
       </c>
       <c r="C39" t="str">
-        <v>飞机</v>
+        <v>n.</v>
       </c>
       <c r="D39" t="str">
-        <v>airplane(飞机)📢</v>
+        <v>拖拉机</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>sour</v>
       </c>
       <c r="B40" t="str">
-        <v>gum</v>
+        <v>/ˈsaʊər/</v>
       </c>
       <c r="C40" t="str">
-        <v>牙龈</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D40" t="str">
-        <v>gum(牙龈)📢</v>
+        <v>酸</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>weight</v>
       </c>
       <c r="B41" t="str">
-        <v>grain</v>
+        <v>/weɪt/</v>
       </c>
       <c r="C41" t="str">
-        <v>谷物</v>
+        <v>n./vt.</v>
       </c>
       <c r="D41" t="str">
-        <v>grain(谷物)📢</v>
+        <v>重量</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>spit</v>
       </c>
       <c r="B42" t="str">
-        <v>needle</v>
+        <v>/spɪt/</v>
       </c>
       <c r="C42" t="str">
-        <v>针</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D42" t="str">
-        <v>needle(针)📢</v>
+        <v>吐</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>scheme</v>
       </c>
       <c r="B43" t="str">
-        <v>tractor</v>
+        <v>/skiːm/</v>
       </c>
       <c r="C43" t="str">
-        <v>拖拉机</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D43" t="str">
-        <v>tractor(拖拉机)📢</v>
+        <v>计划</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>toast</v>
       </c>
       <c r="B44" t="str">
-        <v>prevail</v>
+        <v>/toʊst/</v>
       </c>
       <c r="C44" t="str">
-        <v>盛行</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D44" t="str">
-        <v>prevail(盛行)📢</v>
+        <v>干杯</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>romantic</v>
       </c>
       <c r="B45" t="str">
-        <v>sour</v>
+        <v>/roʊˈmæntɪk/</v>
       </c>
       <c r="C45" t="str">
-        <v>酸</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D45" t="str">
-        <v>sour(酸)📢</v>
+        <v>浪漫的</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>distribution</v>
       </c>
       <c r="B46" t="str">
-        <v>weight</v>
+        <v>/ˌdɪstrɪˈbjuːʃn/</v>
       </c>
       <c r="C46" t="str">
-        <v>重量</v>
+        <v>n.</v>
       </c>
       <c r="D46" t="str">
-        <v>weight(重量)📢</v>
+        <v>分布</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>exercise</v>
       </c>
       <c r="B47" t="str">
-        <v>spit</v>
+        <v>/ˈeksərsaɪz/</v>
       </c>
       <c r="C47" t="str">
-        <v>吐</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D47" t="str">
-        <v>spit(吐)📢</v>
+        <v>运动</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>skim</v>
       </c>
       <c r="B48" t="str">
-        <v>scheme</v>
+        <v>/skɪm/</v>
       </c>
       <c r="C48" t="str">
-        <v>计划</v>
+        <v>v.</v>
       </c>
       <c r="D48" t="str">
-        <v>scheme(计划)📢</v>
+        <v>掠过</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>happen</v>
       </c>
       <c r="B49" t="str">
-        <v>toast</v>
+        <v>/ˈhæpən/</v>
       </c>
       <c r="C49" t="str">
-        <v>干杯</v>
+        <v>vi.</v>
       </c>
       <c r="D49" t="str">
-        <v>toast(干杯)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>romantic</v>
-      </c>
-      <c r="C50" t="str">
-        <v>浪漫的</v>
-      </c>
-      <c r="D50" t="str">
-        <v>romantic(浪漫的)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>romantic</v>
-      </c>
-      <c r="C51" t="str">
-        <v>浪漫的</v>
-      </c>
-      <c r="D51" t="str">
-        <v>romantic(浪漫的)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>leading</v>
-      </c>
-      <c r="C52" t="str">
-        <v>领导</v>
-      </c>
-      <c r="D52" t="str">
-        <v>leading(领导)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>distribution</v>
-      </c>
-      <c r="C53" t="str">
-        <v>分布</v>
-      </c>
-      <c r="D53" t="str">
-        <v>distribution(分布)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>product</v>
-      </c>
-      <c r="C54" t="str">
-        <v>产品</v>
-      </c>
-      <c r="D54" t="str">
-        <v>product(产品)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>congress</v>
-      </c>
-      <c r="C55" t="str">
-        <v>代表大会</v>
-      </c>
-      <c r="D55" t="str">
-        <v>congress(代表大会)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>exercise</v>
-      </c>
-      <c r="C56" t="str">
-        <v>运动</v>
-      </c>
-      <c r="D56" t="str">
-        <v>exercise(运动)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>skim</v>
-      </c>
-      <c r="C57" t="str">
-        <v>掠过</v>
-      </c>
-      <c r="D57" t="str">
-        <v>skim(掠过)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>happen</v>
-      </c>
-      <c r="C58" t="str">
         <v>发生</v>
-      </c>
-      <c r="D58" t="str">
-        <v>happen(发生)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>twice</v>
-      </c>
-      <c r="C59" t="str">
-        <v>两次</v>
-      </c>
-      <c r="D59" t="str">
-        <v>twice(两次)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D59"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D49"/>
   </ignoredErrors>
 </worksheet>
 </file>